--- a/GameConfig/Datas/回复选项配置表.xlsx
+++ b/GameConfig/Datas/回复选项配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="回复选项配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="回复选项配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,41 @@
           <t>affectionRules</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nextNodeId</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>isSessionEnd</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>affectionNpcId</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>affectionDelta</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>optionSetId</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>displayOrder</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>actionIds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -502,6 +537,41 @@
           <t>(list#sep=;),EmotionAffectionRule</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +614,41 @@
           <t>c</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -586,38 +691,1789 @@
           <t>情绪好感规则(元素;分隔,字段,分隔)</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>选项后继节点</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>选项结束Session</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>好感变化对应NPC</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NPC好感变化值</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>回复所属选项集</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>回复显示顺序</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>回复选择动作</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>O011101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>你还记得那一天吗？</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>你似乎想起了什么……</t>
+          <t>这件目前状态不乐观，至少得14天</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M01,M02</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>T0112</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>O01110</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>O011102</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>换件、装配、调试、翻新，保守需要两周</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>T0113</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>O01110</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>O013301</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>该物为全框老花镜，经过多次修缮，尚且可用，但功能大打折扣，判定为【低效品】，建议丢弃。</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>O01330</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>O013302</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>该物为全框老花镜，经过多次修缮，尚且可用，但功能大打折扣，判定为【低效品】，受不知名不可量化“情感”因素影响，升为【中等价值物品】，建议物主自行判定。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>M03</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>E01,E02</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>M03</t>
-        </is>
-      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>O01330</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>O020101</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>我还内置了物品找寻功能，你现在有什么需要帮助的？</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>O02010</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>O020601</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>物品寻找并估值完毕，任务完成，结论：无法使用，建议丢弃。</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>O02060</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>O020602</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>物品寻找并估值完毕，任务完成，结论：无法使用。你为何留下它？</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>M06</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>O02060</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>O030201</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>物品能否替代，不该只由维修成本决定。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>你想起了布偶被抱在怀里的样子……</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>E01,E04</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>T0303</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>O03020</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>O030202</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>从成本和状态看，更换是风险更低的方案。</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>T0304</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>O03020</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>O030501</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>里面有小满留下的纸条。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>也许布偶里还藏着一段和小满有关的记忆。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E03,E04</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>T0306</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>O03050</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>O030502</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>先把破口补好，让它继续陪着你。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>T0307</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>O03050</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O040201</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>先分别记录读取模块和存储部分的状态。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>收音机的存储部分也许还保存着重要内容。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>T0403</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>O04020</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>O040202</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>先尝试接通读取模块，确认能否读取。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>你已经检查过收音机的内部结构。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>T0404</t>
+        </is>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>O04020</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>O040501</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>停下维修，保护仍完好的存储部分。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>T0406</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>O04050</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>O040502</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>再试一次，但先记录可能造成的风险。</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>你记得读取模块的线路并不稳定。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>T0407</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>O04050</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>O050201</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>问她，录音里保存的是什么。</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>收音机的存储部分似乎还完好。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>T0503</t>
+        </is>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>O05020</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>O050202</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>告诉她你愿意听，但不必现在说出来。</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>T0504</t>
+        </is>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>O05020</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>O050501</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>它已经成了你们全家共同期待的一件事。</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>E01,E02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>T0506</t>
+        </is>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>O05050</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>O050502</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>先完成眼前能做的维修，再决定下一步。</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>E00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>T0507</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>O05050</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>O060201</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>先告诉我，那段声音为什么对你重要。</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>老周的收音机里还留有一段声音。</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>T0603</t>
+        </is>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>O06020</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>O060202</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>先检查它还能否在拆件后继续播放。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>T0604</t>
+        </is>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>O06020</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>O060501</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>如果你已经想好了，我会帮你记录这次选择。</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>你知道这段声音一直被老周留着。</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>E01,E03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>T0606</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>O06050</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>O060502</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>再考虑一次，拆下它就不能再播放了。</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>T0607</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>O06050</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>O070201</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>听完。既然他们都来了，就一起听这段录音。</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>你知道收音机里保存着一段家庭录音。</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>E02,E04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>T0703</t>
+        </is>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>O07020</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>O070202</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>先问问每个人是否都准备好了。</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>T0704</t>
+        </is>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>O07020</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>O070501</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>录音里的停顿也许同样重要，再听一遍。</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>录音里的称呼让你想起陈果说过的话。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>M19</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>E04,E03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>M22</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>T0706</t>
+        </is>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>O07050</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>O070502</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>先停在这里，让他们自己决定要不要继续。</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>M22</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>T0707</t>
+        </is>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>O07050</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>O080201</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>先按最近使用的记录排列。</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>E00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>M23,M24,M25,M26,M27</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>T0803</t>
+        </is>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>O08020</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>O080202</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>先看哪些经历彼此产生了联系。</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>E01,E04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>M23,M24,M25,M26,M27</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>T0804</t>
+        </is>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>O08020</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>O080501</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>把记忆清单交给我，我自己决定。</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>T0806</t>
+        </is>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>O08050</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>O080502</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>暂时不用排序，我会逐条检查。</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>T0807</t>
+        </is>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>O08050</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>O090201</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>我找不到那段记录，但愿意听你重新讲。</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>M28</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>T0904</t>
+        </is>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>O09020</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>O090202</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>我还记得小满留下的纸条。</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>E03,E04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>M28</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>T0903</t>
+        </is>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>O09020</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>O090501</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>因为你还没有讲完。</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>你记得有人曾把朋友的声音留在收音机里。</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>E01,E03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>M29</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>T0906</t>
+        </is>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>O09050</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>O090502</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>我不知道原因，但我想继续听。</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>M29</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>T0907</t>
+        </is>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>O09050</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>O100201</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>按维修成本、运输时间和可用状态给旧物排序。</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>E00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>M30,M31</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>T1003</t>
+        </is>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>O10020</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>O100202</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>先问每个人最想带走哪一件，再安排转运。</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>E01,E04</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>M30,M31</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>T1004</t>
+        </is>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>O10020</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>O100501</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>这是我按现有记录算出的结果。</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>E00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>M30,M31</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>T1006</t>
+        </is>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>O10050</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>O100502</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>我说不清全部原因，但我愿意承担这个选择。</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>E01,E05</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>M30,M31</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>T1007</t>
+        </is>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>O10050</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GameConfig/Datas/回复选项配置表.xlsx
+++ b/GameConfig/Datas/回复选项配置表.xlsx
@@ -46,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,8 +413,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -728,6 +741,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>O011101</t>
@@ -735,25 +749,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>这件目前状态不乐观，至少得14天</t>
-        </is>
-      </c>
+          <t>评估完毕，一件至少需要14天。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>T0112</t>
-        </is>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
+          <t>T0136</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>陈先生</t>
+          <t>老周</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -767,8 +787,10 @@
       <c r="N5" t="n">
         <v>1</v>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>O011102</t>
@@ -776,25 +798,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>换件、装配、调试、翻新，保守需要两周</t>
-        </is>
-      </c>
+          <t>换件、装配、调试、翻新，保守需要两周。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>T0113</t>
-        </is>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
+          <t>T0136</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>陈先生</t>
+          <t>老周</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -808,8 +836,10 @@
       <c r="N6" t="n">
         <v>2</v>
       </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>O013301</t>
@@ -820,9 +850,18 @@
           <t>该物为全框老花镜，经过多次修缮，尚且可用，但功能大打折扣，判定为【低效品】，建议丢弃。</t>
         </is>
       </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -834,8 +873,10 @@
       <c r="N7" t="n">
         <v>1</v>
       </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>O013302</t>
@@ -843,9 +884,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>该物为全框老花镜，经过多次修缮，尚且可用，但功能大打折扣，判定为【低效品】，受不知名不可量化“情感”因素影响，升为【中等价值物品】，建议物主自行判定。</t>
-        </is>
-      </c>
+          <t>该物为全框老花镜，经过多次修缮，尚且可用，但功能大打折扣，判定为【低效品】，受不知名不可量化“情感”因素影响，升为【中等价值物品】，建议由物主自行判定。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>M03</t>
@@ -853,15 +895,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>E01,E02</t>
-        </is>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>陈先生</t>
+          <t>老周</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -875,8 +922,10 @@
       <c r="N8" t="n">
         <v>2</v>
       </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>O020101</t>
@@ -884,12 +933,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>我还内置了物品找寻功能，你现在有什么需要帮助的？</t>
-        </is>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
+          <t>$PlayerName已内置物品找寻功能，请吩咐。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -901,8 +959,10 @@
       <c r="N9" t="n">
         <v>1</v>
       </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>O020601</t>
@@ -913,9 +973,18 @@
           <t>物品寻找并估值完毕，任务完成，结论：无法使用，建议丢弃。</t>
         </is>
       </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -927,8 +996,10 @@
       <c r="N10" t="n">
         <v>1</v>
       </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>O020602</t>
@@ -939,9 +1010,10 @@
           <t>物品寻找并估值完毕，任务完成，结论：无法使用。你为何留下它？</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>M02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -949,9 +1021,15 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -963,1517 +1041,941 @@
       <c r="N11" t="n">
         <v>2</v>
       </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>O030201</t>
+          <t>O031501</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>物品能否替代，不该只由维修成本决定。</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>你想起了布偶被抱在怀里的样子……</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>E01,E04</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>M09</t>
-        </is>
-      </c>
+          <t>娃娃崭新度13%，强拆大概率导致永久损毁，建议封存记忆，永不查看。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>T0303</t>
-        </is>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>陈果</t>
-        </is>
-      </c>
+          <t>T0316</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>O03020</t>
+          <t>O03150</t>
         </is>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>O030202</t>
+          <t>O031502</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>从成本和状态看，更换是风险更低的方案。</t>
-        </is>
-      </c>
+          <t>回忆是珍贵的，已检测到不可量化情感浓度，建议打开查看，若无法修复，可寻修理铺修理。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>T0304</t>
-        </is>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>陈果</t>
-        </is>
-      </c>
+          <t>T0319</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>O03020</t>
+          <t>O03150</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>2</v>
       </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>O030501</t>
+          <t>O032901</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>里面有小满留下的纸条。</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>也许布偶里还藏着一段和小满有关的记忆。</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>M08</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>E03,E04</t>
-        </is>
-      </c>
+          <t>直接翻新，大面积拆线换棉，清洗内衬布料，加固所都受力缝合处，完全重新缝合，修复后手感和外观都接近新娃娃。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>T0306</t>
-        </is>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>陈果</t>
-        </is>
-      </c>
+          <t>T0330</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>O03050</t>
+          <t>O03290</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>O030502</t>
+          <t>O032902</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>先把破口补好，让它继续陪着你。</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
+          <t>可以做局部清洁、用纺织颜料补色，保持玩偶原先的样式，就像小满把它送给你时一样。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>T0307</t>
-        </is>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>陈果</t>
-        </is>
-      </c>
+          <t>T0331</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>O03050</t>
+          <t>O03290</t>
         </is>
       </c>
       <c r="N15" t="n">
         <v>2</v>
       </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>O040201</t>
+          <t>O040901</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>先分别记录读取模块和存储部分的状态。</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>收音机的存储部分也许还保存着重要内容。</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
+          <t>无法启动，能效低于基线，功能可替代，判定为低效物。建议丢弃。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>T0403</t>
-        </is>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0410</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>O04020</t>
+          <t>O04090</t>
         </is>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>O040202</t>
+          <t>O040902</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>先尝试接通读取模块，确认能否读取。</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>你已经检查过收音机的内部结构。</t>
-        </is>
-      </c>
+          <t>检测到磁带内有不可量化情感浓度，建议物主自行决定，必要时可强拆收音机仅留磁带。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>T0404</t>
-        </is>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0417</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>O04020</t>
+          <t>O04090</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>2</v>
       </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>O040501</t>
+          <t>O043001</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>停下维修，保护仍完好的存储部分。</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
+          <t>若无更佳替代方案，磁带仓无法打开，磁带无法取出。</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>T0406</t>
-        </is>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0431</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>O04050</t>
+          <t>O04300</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>O040502</t>
+          <t>O043002</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>再试一次，但先记录可能造成的风险。</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>你记得读取模块的线路并不稳定。</t>
-        </is>
-      </c>
+          <t>可以试着去修理铺碰碰运气，老周可能有些现在停产了的旧零件。</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>T0407</t>
-        </is>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0431</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>O04050</t>
+          <t>O04300</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>2</v>
       </c>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>O050201</t>
+          <t>O043101</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>问她，录音里保存的是什么。</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>收音机的存储部分似乎还完好。</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
+          <t>这与您的收音机不相关，您求助于他，是以顾客而非监督员的身份。</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>T0503</t>
-        </is>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0432</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>O05020</t>
+          <t>O04310</t>
         </is>
       </c>
       <c r="N20" t="n">
         <v>1</v>
       </c>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>O050202</t>
+          <t>O043102</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>告诉她你愿意听，但不必现在说出来。</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
+          <t>我能理解，但您也说，收音机里的东西您放不下，那么这是否值得您为其赌一把呢？</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>T0504</t>
-        </is>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0432</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>O05020</t>
+          <t>O04310</t>
         </is>
       </c>
       <c r="N21" t="n">
         <v>2</v>
       </c>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>O050501</t>
+          <t>O043401</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>它已经成了你们全家共同期待的一件事。</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>E01,E02</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>T0506</t>
-        </is>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>我的能力范围只包括物件评估，不包括对记忆的判断。</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>O05050</t>
+          <t>O04340</t>
         </is>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>O050502</t>
+          <t>O043402</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>先完成眼前能做的维修，再决定下一步。</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>E00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>T0507</t>
-        </is>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>人类有记住所经之事、所爱之人的本能，所以“记忆”大概的确是值得人类为之去留下些什么的。</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>M10,M16</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>O05050</t>
+          <t>O04340</t>
         </is>
       </c>
       <c r="N23" t="n">
         <v>2</v>
       </c>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>O060201</t>
+          <t>O051201</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>先告诉我，那段声音为什么对你重要。</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>老周的收音机里还留有一段声音。</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>M16</t>
-        </is>
-      </c>
+          <t>出仓机构齿轮零件。</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>T0603</t>
-        </is>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
+          <t>T0513</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>O06020</t>
+          <t>O05120</t>
         </is>
       </c>
       <c r="N24" t="n">
         <v>1</v>
       </c>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>O060202</t>
+          <t>O051202</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>先检查它还能否在拆件后继续播放。</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
+          <t>出仓机构齿轮零件。我记得您的座钟里也有类似的零件。</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>T0604</t>
-        </is>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
+          <t>T0514</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>O06020</t>
+          <t>O05120</t>
         </is>
       </c>
       <c r="N25" t="n">
         <v>2</v>
       </c>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>O060501</t>
+          <t>O060701</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>如果你已经想好了，我会帮你记录这次选择。</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>你知道这段声音一直被老周留着。</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>M17</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>E01,E03</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>M18</t>
-        </is>
-      </c>
+          <t>磁带记录时间为2017年3月25日，距今久远，磁带内部受潮发霉，可能出现音质问题。</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>T0606</t>
-        </is>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
+          <t>T0608</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>O06050</t>
+          <t>O06070</t>
         </is>
       </c>
       <c r="N26" t="n">
         <v>1</v>
       </c>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>O060502</t>
+          <t>O060702</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>再考虑一次，拆下它就不能再播放了。</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>M18</t>
-        </is>
-      </c>
+          <t>磁带记录时间为2017年3月25日，距今久远，不过大概是个很重要的时间点。您的记忆里有和这个时间挂钩的事情吗？</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>T0607</t>
-        </is>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
+          <t>T0608</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>O06050</t>
+          <t>O06070</t>
         </is>
       </c>
       <c r="N27" t="n">
         <v>2</v>
       </c>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>O070201</t>
+          <t>O064601</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>听完。既然他们都来了，就一起听这段录音。</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>你知道收音机里保存着一段家庭录音。</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>E02,E04</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>M21</t>
-        </is>
-      </c>
+          <t>我只是一个用于物品评估和价值估量的人工智能，无法判定情感。</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>T0703</t>
-        </is>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0647</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>O07020</t>
+          <t>O06460</t>
         </is>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>O070202</t>
+          <t>O064602</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>先问问每个人是否都准备好了。</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>M21</t>
-        </is>
-      </c>
+          <t>我……似乎有点理解，什么是“情感”了。</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>M12,M18</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>T0704</t>
-        </is>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0648</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>O07020</t>
+          <t>O06460</t>
         </is>
       </c>
       <c r="N29" t="n">
         <v>2</v>
       </c>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>O070501</t>
+          <t>O070701</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>录音里的停顿也许同样重要，再听一遍。</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>录音里的称呼让你想起陈果说过的话。</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>M19</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>E04,E03</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>M22</t>
-        </is>
-      </c>
+          <t>高效代替低效，本就是最正常的事情。没什么好为我可惜的。</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>T0706</t>
-        </is>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>陈果</t>
-        </is>
-      </c>
+          <t>T0708</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>O07050</t>
+          <t>O07070</t>
         </is>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>O070502</t>
+          <t>O070702</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>先停在这里，让他们自己决定要不要继续。</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>M22</t>
-        </is>
-      </c>
+          <t>怎么想的？……实话说，有点……难受？闷闷的，说不上来是什么感觉……</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>M19</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>T0707</t>
-        </is>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
+          <t>T0709</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>O07050</t>
+          <t>O07070</t>
         </is>
       </c>
       <c r="N31" t="n">
         <v>2</v>
       </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>O080201</t>
+          <t>O071601</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>先按最近使用的记录排列。</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>E00</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>M23,M24,M25,M26,M27</t>
-        </is>
-      </c>
+          <t>删除全部记忆？……既然是没法拒绝的命令，再不舍也要做啊。</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>T0803</t>
-        </is>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
+          <t>T0717</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>O08020</t>
+          <t>O07160</t>
         </is>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>O080202</t>
+          <t>O071602</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>先看哪些经历彼此产生了联系。</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>E01,E04</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>M23,M24,M25,M26,M27</t>
-        </is>
-      </c>
+          <t>……没关系的，如果什么都忘了，再重新学一次，也是帮您、帮果果、帮周老重新回忆一次。就像那个磁带里的录音，不也帮您想到了那时吗？</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>T0804</t>
-        </is>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
+          <t>T0719</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>O08020</t>
+          <t>O07160</t>
         </is>
       </c>
       <c r="N33" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>O080501</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>把记忆清单交给我，我自己决定。</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>T0806</t>
-        </is>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>O08050</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>O080502</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>暂时不用排序，我会逐条检查。</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>T0807</t>
-        </is>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>O08050</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>O090201</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>我找不到那段记录，但愿意听你重新讲。</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>M28</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>T0904</t>
-        </is>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>O09020</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>O090202</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>我还记得小满留下的纸条。</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>M08</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>E03,E04</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>M28</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>T0903</t>
-        </is>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>O09020</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>O090501</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>因为你还没有讲完。</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>你记得有人曾把朋友的声音留在收音机里。</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>M17</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>E01,E03</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>M29</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>T0906</t>
-        </is>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>O09050</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>O090502</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>我不知道原因，但我想继续听。</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>M29</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>T0907</t>
-        </is>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>O09050</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>O100201</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>按维修成本、运输时间和可用状态给旧物排序。</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>E00</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>M30,M31</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>T1003</t>
-        </is>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>O10020</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>O100202</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>先问每个人最想带走哪一件，再安排转运。</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>E01,E04</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>M30,M31</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>T1004</t>
-        </is>
-      </c>
-      <c r="J41" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>O10020</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>O100501</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>这是我按现有记录算出的结果。</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>E00</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>M30,M31</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>T1006</t>
-        </is>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>O10050</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>O100502</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>我说不清全部原因，但我愿意承担这个选择。</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>E01,E05</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>M30,M31</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>T1007</t>
-        </is>
-      </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>2</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>O10050</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>2</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GameConfig/Datas/回复选项配置表.xlsx
+++ b/GameConfig/Datas/回复选项配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="回复选项配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="回复选项配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -741,7 +741,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>O011101</t>
@@ -752,15 +751,11 @@
           <t>评估完毕，一件至少需要14天。</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>T0136</t>
@@ -787,10 +782,8 @@
       <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>O011102</t>
@@ -801,15 +794,11 @@
           <t>换件、装配、调试、翻新，保守需要两周。</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>T0136</t>
@@ -836,10 +825,8 @@
       <c r="N6" t="n">
         <v>2</v>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>O013301</t>
@@ -850,18 +837,11 @@
           <t>该物为全框老花镜，经过多次修缮，尚且可用，但功能大打折扣，判定为【低效品】，建议丢弃。</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -873,10 +853,8 @@
       <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>O013302</t>
@@ -887,7 +865,6 @@
           <t>该物为全框老花镜，经过多次修缮，尚且可用，但功能大打折扣，判定为【低效品】，受不知名不可量化“情感”因素影响，升为【中等价值物品】，建议由物主自行判定。</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>M03</t>
@@ -898,9 +875,6 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>True</t>
@@ -922,10 +896,8 @@
       <c r="N8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>O020101</t>
@@ -936,18 +908,11 @@
           <t>$PlayerName已内置物品找寻功能，请吩咐。</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -959,10 +924,8 @@
       <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>O020601</t>
@@ -973,18 +936,11 @@
           <t>物品寻找并估值完毕，任务完成，结论：无法使用，建议丢弃。</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -996,10 +952,8 @@
       <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>O020602</t>
@@ -1010,7 +964,6 @@
           <t>物品寻找并估值完毕，任务完成，结论：无法使用。你为何留下它？</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>M02</t>
@@ -1021,15 +974,11 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -1041,10 +990,8 @@
       <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>O031501</t>
@@ -1055,11 +1002,6 @@
           <t>娃娃崭新度13%，强拆大概率导致永久损毁，建议封存记忆，永不查看。</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>T0316</t>
@@ -1070,7 +1012,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>0</v>
       </c>
@@ -1082,10 +1023,8 @@
       <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>O031502</t>
@@ -1096,11 +1035,16 @@
           <t>回忆是珍贵的，已检测到不可量化情感浓度，建议打开查看，若无法修复，可寻修理铺修理。</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>（需要先发现玩偶腹部里的东西）</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>T0319</t>
@@ -1111,7 +1055,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -1123,28 +1066,26 @@
       <c r="N13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>O032901</t>
+          <t>O032401</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>直接翻新，大面积拆线换棉，清洗内衬布料，加固所都受力缝合处，完全重新缝合，修复后手感和外观都接近新娃娃。</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+          <t>（去老周的修理铺）</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E00</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>T0330</t>
+          <t>T0325</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1152,830 +1093,717 @@
           <t>False</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>O03290</t>
+          <t>O03240</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
+          <t>O032901</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>直接翻新，大面积拆线换棉，清洗内衬布料，加固所都受力缝合处，完全重新缝合，修复后手感和外观都接近新娃娃。</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>T0330</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>O03290</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
           <t>O032902</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>可以做局部清洁、用纺织颜料补色，保持玩偶原先的样式，就像小满把它送给你时一样。</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>T0331</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>O03290</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>O040901</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>无法启动，能效低于基线，功能可替代，判定为低效物。建议丢弃。</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>T0410</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>O04090</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>O040902</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>检测到磁带内有不可量化情感浓度，建议物主自行决定，必要时可强拆收音机仅留磁带。</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>T0417</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>O04090</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>O043001</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>若无更佳替代方案，磁带仓无法打开，磁带无法取出。</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>T0431</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>O04300</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>O043002</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>可以试着去修理铺碰碰运气，老周可能有些现在停产了的旧零件。</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>M17</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>T0431</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>O04300</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="N20" t="n">
         <v>2</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>O043101</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>这与您的收音机不相关，您求助于他，是以顾客而非监督员的身份。</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>T0432</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>O04310</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>O043102</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>我能理解，但您也说，收音机里的东西您放不下，那么这是否值得您为其赌一把呢？</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>T0432</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>O04310</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>2</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>O043401</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>我的能力范围只包括物件评估，不包括对记忆的判断。</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>O04340</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>O043402</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>人类有记住所经之事、所爱之人的本能，所以“记忆”大概的确是值得人类为之去留下些什么的。</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>M10,M16</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>O04340</t>
         </is>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>2</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
         <is>
           <t>O051201</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>出仓机构齿轮零件。</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>T0513</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>O05120</t>
         </is>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
         <is>
           <t>O051202</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>出仓机构齿轮零件。我记得您的座钟里也有类似的零件。</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>M08</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>T0514</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>O05120</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>2</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
         <is>
           <t>O060701</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>磁带记录时间为2017年3月25日，距今久远，磁带内部受潮发霉，可能出现音质问题。</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>T0608</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>O06070</t>
         </is>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
         <is>
           <t>O060702</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>磁带记录时间为2017年3月25日，距今久远，不过大概是个很重要的时间点。您的记忆里有和这个时间挂钩的事情吗？</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>T0608</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>O06070</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
         <is>
           <t>O064601</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>我只是一个用于物品评估和价值估量的人工智能，无法判定情感。</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>T0647</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>O06460</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
         <is>
           <t>O064602</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>我……似乎有点理解，什么是“情感”了。</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>M12,M18</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>T0648</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>O06460</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
         <is>
           <t>O070701</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>高效代替低效，本就是最正常的事情。没什么好为我可惜的。</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>T0708</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>O07070</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>O070702</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>怎么想的？……实话说，有点……难受？闷闷的，说不上来是什么感觉……</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>M19</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>T0709</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>O07070</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
         <is>
           <t>O071601</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>删除全部记忆？……既然是没法拒绝的命令，再不舍也要做啊。</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>T0717</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>O07160</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="N33" t="n">
         <v>1</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
         <is>
           <t>O071602</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>……没关系的，如果什么都忘了，再重新学一次，也是帮您、帮果果、帮周老重新回忆一次。就像那个磁带里的录音，不也帮您想到了那时吗？</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>M18</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>T0719</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>O07160</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="N34" t="n">
         <v>2</v>
       </c>
-      <c r="O33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
